--- a/aq_files/0617.xlsx
+++ b/aq_files/0617.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List_Basics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,468 +413,508 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Q#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Options (if MCQ)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>List is:</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A) mutable B) immutable C) none D) both</t>
+          <t>What command is used to list all topics in a Kafka cluster?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>A) kafka-topics --list B) kafka-list --topics C) kafka-admin --topics D) kafka-topics --show</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Index starts from:</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A) 0 B) 1 C) -1 D) none</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A topic has a replication factor of 3 but one replica is out of sync. What command would you use to check the ISR status?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Find running sum of array.</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>What tool is used to monitor consumer lag?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Move zeroes to end.</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>What is the preferred way to increase partitions for a topic?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) Delete and recreate B) Use kafka-topics --alter C) Stop cluster and edit config D) Cannot increase partitions</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rotate list by k positions.</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>A broker is being decommissioned. What is the safe process to migrate partitions?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Find maximum subarray sum.</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>What JMX metric indicates the rate of messages being produced?</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Find missing number in list.</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>Which command checks broker health?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) kafka-broker-health B) kafka-broker-api-versions C) kafka-health-check D) kafka-status</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Check sorted list.</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Consumer lag is increasing rapidly. What are two possible causes?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reverse list in-place.</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>What is the utility to mirror data between clusters?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Find pair with target sum.</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>What does the command "kafka-log-dirs --describe --broker 0" show?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) Consumer offsets B) Log directory usage per broker C) Topic partitions D) Producer metrics</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Remove element from list.</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>What is the preferred backup strategy for Kafka?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Find intersection of sorted lists.</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>A disk is filling up quickly. What two operational changes can you make without downtime?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Find longest increasing subsequence (basic).</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>Which tool is used for load balancing partitions?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>A) kafka-rebalance B) kafka-reassign-partitions C) kafka-balance D) kafka-partition-move</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Split list into chunks.</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>What command is used to delete a consumer group?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Flatten nested list.</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>How do you upgrade a Kafka cluster without downtime?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>A) Stop all brokers at once B) Rolling upgrade C) Reinstall all D) Cannot upgrade without downtime</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Find first non-repeating element.</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>A broker fails and cannot be recovered. How do you ensure the replicas on other brokers become leaders?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Check if list contains duplicates.</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>What metric indicates disk read operations per second?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Merge sorted lists.</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>What is the correct order to stop a Kafka cluster?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A) Stop brokers, then Zookeeper B) Stop Zookeeper, then brokers C) Stop both simultaneously D) Order doesn't matter</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Find peak element.</t>
+          <t>One Word</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>What operational concept describes adding new brokers to increase capacity?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Find subarray with given sum.</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>You need to monitor if any brokers are under-replicated. What command gives you this information?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
